--- a/downloads/korrigierte_referenz/Sprachkurse_3NF.xlsx
+++ b/downloads/korrigierte_referenz/Sprachkurse_3NF.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PERSON" sheetId="1" r:id="R3c2c476fc5d44d99"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ABTEILUNG" sheetId="2" r:id="R0f21944ea3d547c4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SPRACHKENNTNIS" sheetId="3" r:id="R2b4a850df4804cde"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PERSON" sheetId="1" r:id="Re83c932bb8684247"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ABTEILUNG" sheetId="2" r:id="R3ba02a6a5827496a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SPRACHKENNTNIS" sheetId="3" r:id="R25bf9c01fe7549fb"/>
   </x:sheets>
 </x:workbook>
 </file>
